--- a/RAW_DATA_XLSX/LKA_raw_data.xlsx
+++ b/RAW_DATA_XLSX/LKA_raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,52 +429,57 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>BX.KLT.DINV.WD.GD.ZS</t>
+          <t>education</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>FP.CPI.TOTL.ZG</t>
+          <t>fdi</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>NE.TRD.GNFS.ZS</t>
+          <t>gdp_growth</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>NV.IND.TOTL.ZS</t>
+          <t>gdp_pc</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>NY.GDP.MKTP.KD.ZG</t>
+          <t>log_gdp_pc</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>NY.GDP.PCAP.KD</t>
+          <t>gini</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>SE.SEC.ENRR</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>SI.POV.GINI</t>
+          <t>inflation</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>SL.UEM.TOTL.ZS</t>
+          <t>trade</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>SP.URB.TOTL.IN.ZS</t>
+          <t>unemployment</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>urban</t>
         </is>
       </c>
     </row>
@@ -488,33 +493,36 @@
         <v>1995</v>
       </c>
       <c r="C2" t="n">
+        <v>87.1477432250977</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.42975354803099</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>5.5000852341585</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1681.35053208093</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.427352637595704</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>26.6839789029789</v>
+      </c>
+      <c r="J2" t="n">
         <v>7.67484873449805</v>
       </c>
-      <c r="E2" t="n">
+      <c r="K2" t="n">
         <v>81.6350490886111</v>
       </c>
-      <c r="F2" t="n">
-        <v>26.6839789029789</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5.5000852341585</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1681.35053208093</v>
-      </c>
-      <c r="I2" t="n">
-        <v>87.1477432250977</v>
-      </c>
-      <c r="J2" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>12.27</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>15.8652068539762</v>
       </c>
     </row>
@@ -527,30 +535,33 @@
       <c r="B3" t="n">
         <v>1996</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
         <v>0.862545735590984</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>3.79996720568178</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1712.00815802791</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.445422321893552</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>26.5742275506166</v>
+      </c>
+      <c r="J3" t="n">
         <v>15.9358310447214</v>
       </c>
-      <c r="E3" t="n">
+      <c r="K3" t="n">
         <v>78.87396371438091</v>
       </c>
-      <c r="F3" t="n">
-        <v>26.5742275506166</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.79996720568178</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1712.00815802791</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>11.35</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>15.5065242809941</v>
       </c>
     </row>
@@ -563,30 +574,33 @@
       <c r="B4" t="n">
         <v>1997</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
         <v>2.84957994822129</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>6.40539969571286</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1787.41017985524</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.488523024273604</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>26.9936625997448</v>
+      </c>
+      <c r="J4" t="n">
         <v>9.57369626405162</v>
       </c>
-      <c r="E4" t="n">
+      <c r="K4" t="n">
         <v>80.1375533095503</v>
       </c>
-      <c r="F4" t="n">
-        <v>26.9936625997448</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.40539969571286</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1787.41017985524</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>10.6</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>15.1948401614719</v>
       </c>
     </row>
@@ -599,30 +613,33 @@
       <c r="B5" t="n">
         <v>1998</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
         <v>1.22725240374875</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>4.69842304772052</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1836.38946262206</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.515556674296123</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>27.6167149449992</v>
+      </c>
+      <c r="J5" t="n">
         <v>9.364243006832289</v>
       </c>
-      <c r="E5" t="n">
+      <c r="K5" t="n">
         <v>78.4949891255872</v>
       </c>
-      <c r="F5" t="n">
-        <v>27.6167149449992</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.69842304772052</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1836.38946262206</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9.17</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>14.9379455930521</v>
       </c>
     </row>
@@ -635,30 +652,33 @@
       <c r="B6" t="n">
         <v>1999</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
         <v>1.12277824473328</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>4.30054049813373</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1880.1067802774</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.539083852230942</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>27.3613237332533</v>
+      </c>
+      <c r="J6" t="n">
         <v>4.69170563048438</v>
       </c>
-      <c r="E6" t="n">
+      <c r="K6" t="n">
         <v>78.7514783496374</v>
       </c>
-      <c r="F6" t="n">
-        <v>27.3613237332533</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.30054049813373</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1880.1067802774</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>8.880000000000001</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>14.7436316733772</v>
       </c>
     </row>
@@ -671,30 +691,33 @@
       <c r="B7" t="n">
         <v>2000</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
         <v>1.04207418020439</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>6.00003315828934</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1956.93310381072</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.579133783782042</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>27.3180767964657</v>
+      </c>
+      <c r="J7" t="n">
         <v>6.17627591012045</v>
       </c>
-      <c r="E7" t="n">
+      <c r="K7" t="n">
         <v>88.636441704913</v>
       </c>
-      <c r="F7" t="n">
-        <v>27.3180767964657</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.00003315828934</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1956.93310381072</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>7.74</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>14.6196895000898</v>
       </c>
     </row>
@@ -707,30 +730,33 @@
       <c r="B8" t="n">
         <v>2001</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
         <v>1.09074720867871</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>-1.54540813366026</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1896.48251734068</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.547756142705594</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>26.8205944160785</v>
+      </c>
+      <c r="J8" t="n">
         <v>14.15845579912</v>
       </c>
-      <c r="E8" t="n">
+      <c r="K8" t="n">
         <v>80.8986015327576</v>
       </c>
-      <c r="F8" t="n">
-        <v>26.8205944160785</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1.54540813366026</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1896.48251734068</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>7.9</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>14.5739539539707</v>
       </c>
     </row>
@@ -743,32 +769,35 @@
       <c r="B9" t="n">
         <v>2002</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
         <v>1.1882779089504</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>3.96467568513113</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1951.22522777045</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.576212776179776</v>
+      </c>
+      <c r="H9" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>28.0106134516732</v>
+      </c>
+      <c r="J9" t="n">
         <v>9.55103167007251</v>
       </c>
-      <c r="E9" t="n">
+      <c r="K9" t="n">
         <v>76.3351317826517</v>
       </c>
-      <c r="F9" t="n">
-        <v>28.0106134516732</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.96467568513113</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1951.22522777045</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8.76</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>14.6107836754127</v>
       </c>
     </row>
@@ -781,30 +810,33 @@
       <c r="B10" t="n">
         <v>2003</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
         <v>1.21132740876657</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>5.9402690780223</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2052.03045078787</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.626585045745793</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>28.4245704176973</v>
+      </c>
+      <c r="J10" t="n">
         <v>6.31463787051174</v>
       </c>
-      <c r="E10" t="n">
+      <c r="K10" t="n">
         <v>75.336247330543</v>
       </c>
-      <c r="F10" t="n">
-        <v>28.4245704176973</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5.9402690780223</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2052.03045078787</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>14.7256630416211</v>
       </c>
     </row>
@@ -817,30 +849,33 @@
       <c r="B11" t="n">
         <v>2004</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
         <v>1.12667735136244</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>5.44506127885352</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2149.10628588002</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7.672807353716381</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>28.6181015199147</v>
+      </c>
+      <c r="J11" t="n">
         <v>7.57592582995856</v>
       </c>
-      <c r="E11" t="n">
+      <c r="K11" t="n">
         <v>79.4829449011187</v>
       </c>
-      <c r="F11" t="n">
-        <v>28.6181015199147</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5.44506127885352</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2149.10628588002</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>14.9130061059922</v>
       </c>
     </row>
@@ -853,30 +888,33 @@
       <c r="B12" t="n">
         <v>2005</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
         <v>1.11612854301768</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>6.24174804376447</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2268.6880127005</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.726956975414227</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>30.1880884644457</v>
+      </c>
+      <c r="J12" t="n">
         <v>11.6396860971118</v>
       </c>
-      <c r="E12" t="n">
+      <c r="K12" t="n">
         <v>73.6039729580533</v>
       </c>
-      <c r="F12" t="n">
-        <v>30.1880884644457</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6.24174804376447</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2268.6880127005</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>7.67</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>15.167273918248</v>
       </c>
     </row>
@@ -889,32 +927,35 @@
       <c r="B13" t="n">
         <v>2006</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
         <v>1.6970072277349</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>7.66829190107919</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2426.34873273046</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.794142827207227</v>
+      </c>
+      <c r="H13" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>30.6422951801489</v>
+      </c>
+      <c r="J13" t="n">
         <v>10.0201836057035</v>
       </c>
-      <c r="E13" t="n">
+      <c r="K13" t="n">
         <v>71.2611784883009</v>
       </c>
-      <c r="F13" t="n">
-        <v>30.6422951801489</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7.66829190107919</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2426.34873273046</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>6.5</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>15.4829275281105</v>
       </c>
     </row>
@@ -927,30 +968,33 @@
       <c r="B14" t="n">
         <v>2007</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
         <v>1.8639738781084</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>6.79682611892866</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2573.54362192705</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.853039069377382</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>29.9198197775274</v>
+      </c>
+      <c r="J14" t="n">
         <v>15.8421114924843</v>
       </c>
-      <c r="E14" t="n">
+      <c r="K14" t="n">
         <v>68.60651166013911</v>
       </c>
-      <c r="F14" t="n">
-        <v>29.9198197775274</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6.79682611892866</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2573.54362192705</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5.97</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>15.8544279853018</v>
       </c>
     </row>
@@ -963,30 +1007,33 @@
       <c r="B15" t="n">
         <v>2008</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
         <v>1.84752962305149</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>5.95008814473897</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2708.58594222506</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.904181985155768</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>29.3711947494741</v>
+      </c>
+      <c r="J15" t="n">
         <v>22.5644955300126</v>
       </c>
-      <c r="E15" t="n">
+      <c r="K15" t="n">
         <v>63.369043608222</v>
       </c>
-      <c r="F15" t="n">
-        <v>29.3711947494741</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.95008814473897</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2708.58594222506</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>5.22</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>16.2762363395441</v>
       </c>
     </row>
@@ -999,32 +1046,35 @@
       <c r="B16" t="n">
         <v>2009</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
         <v>0.960390452698523</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>3.53891205317842</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2787.27350976338</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.93281916036442</v>
+      </c>
+      <c r="H16" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>29.6714387318411</v>
+      </c>
+      <c r="J16" t="n">
         <v>3.46496322106074</v>
       </c>
-      <c r="E16" t="n">
+      <c r="K16" t="n">
         <v>49.1491415308235</v>
       </c>
-      <c r="F16" t="n">
-        <v>29.6714387318411</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.53891205317842</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2787.27350976338</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5.85</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>16.7428136405592</v>
       </c>
     </row>
@@ -1038,29 +1088,32 @@
         <v>2010</v>
       </c>
       <c r="C17" t="n">
+        <v>92.34970855712891</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.814446069624814</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
+        <v>8.01596737055139</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2993.01411511147</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.004036223882832</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>27.7831982984661</v>
+      </c>
+      <c r="J17" t="n">
         <v>6.2176488930462</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>27.7831982984661</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8.01596737055139</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2993.01411511147</v>
-      </c>
-      <c r="I17" t="n">
-        <v>92.34970855712891</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
         <v>4.784</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>17.2486209380693</v>
       </c>
     </row>
@@ -1074,29 +1127,32 @@
         <v>2011</v>
       </c>
       <c r="C18" t="n">
+        <v>94.108642578125</v>
+      </c>
+      <c r="D18" t="n">
         <v>1.41088360121529</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>8.669483011931399</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3232.37350382301</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8.080971977265621</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>29.0731497643121</v>
+      </c>
+      <c r="J18" t="n">
         <v>6.7167684358854</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>29.0731497643121</v>
-      </c>
-      <c r="G18" t="n">
-        <v>8.669483011931399</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3232.37350382301</v>
-      </c>
-      <c r="I18" t="n">
-        <v>94.108642578125</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
         <v>4.118</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>17.7881192817964</v>
       </c>
     </row>
@@ -1110,31 +1166,34 @@
         <v>2012</v>
       </c>
       <c r="C19" t="n">
+        <v>94.6744689941406</v>
+      </c>
+      <c r="D19" t="n">
         <v>1.3359173422599</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>8.63218137662685</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3484.79049033884</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.156163203837661</v>
+      </c>
+      <c r="H19" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>30.9698538096371</v>
+      </c>
+      <c r="J19" t="n">
         <v>7.54291373239437</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>30.9698538096371</v>
-      </c>
-      <c r="G19" t="n">
-        <v>8.63218137662685</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3484.79049033884</v>
-      </c>
-      <c r="I19" t="n">
-        <v>94.6744689941406</v>
-      </c>
-      <c r="J19" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
         <v>3.88</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>18.2617686748284</v>
       </c>
     </row>
@@ -1148,29 +1207,32 @@
         <v>2013</v>
       </c>
       <c r="C20" t="n">
+        <v>95.14426361963559</v>
+      </c>
+      <c r="D20" t="n">
         <v>1.21148000445532</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>4.05174633027869</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3728.93586647848</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.223878181446445</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>30.7956807273264</v>
+      </c>
+      <c r="J20" t="n">
         <v>6.90845034828452</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
-        <v>30.7956807273264</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4.05174633027869</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3728.93586647848</v>
-      </c>
-      <c r="I20" t="n">
-        <v>95.14426361963559</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
         <v>4.186</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>18.4323136480916</v>
       </c>
     </row>
@@ -1184,29 +1246,32 @@
         <v>2014</v>
       </c>
       <c r="C21" t="n">
+        <v>93.4926277980089</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.08277813761066</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>6.3779788972687</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3929.92062032185</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.276374506267929</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>30.5178954294297</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.1790022823606</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="n">
-        <v>30.5178954294297</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6.3779788972687</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3929.92062032185</v>
-      </c>
-      <c r="I21" t="n">
-        <v>93.4926277980089</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
         <v>4.157</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>18.6153877203724</v>
       </c>
     </row>
@@ -1220,31 +1285,34 @@
         <v>2015</v>
       </c>
       <c r="C22" t="n">
+        <v>94.45169289622859</v>
+      </c>
+      <c r="D22" t="n">
         <v>0.798746315198801</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
+        <v>4.20595547449241</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4057.7158346231</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.308375491966133</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>29.5354178735039</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.76836783062096</v>
       </c>
-      <c r="E22" t="n">
+      <c r="K22" t="n">
         <v>46.9179708088816</v>
       </c>
-      <c r="F22" t="n">
-        <v>29.5354178735039</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.20595547449241</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4057.7158346231</v>
-      </c>
-      <c r="I22" t="n">
-        <v>94.45169289622859</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>4.519</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>18.796256612131</v>
       </c>
     </row>
@@ -1258,33 +1326,36 @@
         <v>2016</v>
       </c>
       <c r="C23" t="n">
+        <v>93.90372212763749</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.01937184461335</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>5.05362488994436</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4214.74117992085</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.346343464024132</v>
+      </c>
+      <c r="H23" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>30.4827177292135</v>
+      </c>
+      <c r="J23" t="n">
         <v>3.9588884659307</v>
       </c>
-      <c r="E23" t="n">
+      <c r="K23" t="n">
         <v>46.4715370252187</v>
       </c>
-      <c r="F23" t="n">
-        <v>30.4827177292135</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5.05362488994436</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4214.74117992085</v>
-      </c>
-      <c r="I23" t="n">
-        <v>93.90372212763749</v>
-      </c>
-      <c r="J23" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>4.242</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>18.9747679368162</v>
       </c>
     </row>
@@ -1298,31 +1369,34 @@
         <v>2017</v>
       </c>
       <c r="C24" t="n">
+        <v>94.0418660922689</v>
+      </c>
+      <c r="D24" t="n">
         <v>1.45462805347273</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
+        <v>6.46068127065753</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4436.00789945768</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.397510129230097</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>31.1282786464433</v>
+      </c>
+      <c r="J24" t="n">
         <v>7.70413767850602</v>
       </c>
-      <c r="E24" t="n">
+      <c r="K24" t="n">
         <v>47.1404098004644</v>
       </c>
-      <c r="F24" t="n">
-        <v>31.1282786464433</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.46068127065753</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4436.00789945768</v>
-      </c>
-      <c r="I24" t="n">
-        <v>94.0418660922689</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>4.046</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>19.1507693078088</v>
       </c>
     </row>
@@ -1336,31 +1410,34 @@
         <v>2018</v>
       </c>
       <c r="C25" t="n">
+        <v>95.91073316939909</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.70888696252001</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>2.31008425545845</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4493.03575444544</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.410283866849634</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>30.0568195254141</v>
+      </c>
+      <c r="J25" t="n">
         <v>2.135037737132</v>
       </c>
-      <c r="E25" t="n">
+      <c r="K25" t="n">
         <v>49.8093967521361</v>
       </c>
-      <c r="F25" t="n">
-        <v>30.0568195254141</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2.31008425545845</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4493.03575444544</v>
-      </c>
-      <c r="I25" t="n">
-        <v>95.91073316939909</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>4.318</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>19.3241083384127</v>
       </c>
     </row>
@@ -1373,32 +1450,35 @@
       <c r="B26" t="n">
         <v>2019</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
         <v>0.835367459152173</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>-0.220483886831275</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4455.78189608267</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8.401957834287735</v>
+      </c>
+      <c r="H26" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>29.1910098710383</v>
+      </c>
+      <c r="J26" t="n">
         <v>3.52839358231811</v>
       </c>
-      <c r="E26" t="n">
+      <c r="K26" t="n">
         <v>49.42552388546</v>
       </c>
-      <c r="F26" t="n">
-        <v>29.1910098710383</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.220483886831275</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4455.78189608267</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>4.67</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>19.4946326418437</v>
       </c>
     </row>
@@ -1411,30 +1491,33 @@
       <c r="B27" t="n">
         <v>2020</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
         <v>0.5147005526676079</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>-4.62451503749502</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4227.23315306594</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8.349302957092942</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>28.235832875126</v>
+      </c>
+      <c r="J27" t="n">
         <v>6.15394508391738</v>
       </c>
-      <c r="E27" t="n">
+      <c r="K27" t="n">
         <v>37.089118857292</v>
       </c>
-      <c r="F27" t="n">
-        <v>28.235832875126</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-4.62451503749502</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4227.23315306594</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5.364</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>19.6621898312161</v>
       </c>
     </row>
@@ -1448,31 +1531,34 @@
         <v>2021</v>
       </c>
       <c r="C28" t="n">
+        <v>89.83396855587939</v>
+      </c>
+      <c r="D28" t="n">
         <v>0.66882570941316</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>4.2074764951157</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4357.97225779491</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8.37976214967313</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>29.9540097663376</v>
+      </c>
+      <c r="J28" t="n">
         <v>7.01478071238195</v>
       </c>
-      <c r="E28" t="n">
+      <c r="K28" t="n">
         <v>41.2288463291999</v>
       </c>
-      <c r="F28" t="n">
-        <v>29.9540097663376</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4.2074764951157</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4357.97225779491</v>
-      </c>
-      <c r="I28" t="n">
-        <v>89.83396855587939</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>4.981</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>19.8266275195269</v>
       </c>
     </row>
@@ -1486,31 +1572,34 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
+        <v>88.1918156520303</v>
+      </c>
+      <c r="D29" t="n">
         <v>1.19249322228342</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
+        <v>-7.34919301306745</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4033.14561476298</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8.302301900039318</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>29.8058315790625</v>
+      </c>
+      <c r="J29" t="n">
         <v>49.7211021114327</v>
       </c>
-      <c r="E29" t="n">
+      <c r="K29" t="n">
         <v>46.6826080196819</v>
       </c>
-      <c r="F29" t="n">
-        <v>29.8058315790625</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-7.34919301306745</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4033.14561476298</v>
-      </c>
-      <c r="I29" t="n">
-        <v>88.1918156520303</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4.528</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>19.9877933196367</v>
       </c>
     </row>
@@ -1524,31 +1613,34 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
+        <v>87.95340653321141</v>
+      </c>
+      <c r="D30" t="n">
         <v>0.851705946554554</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>-2.3298481898334</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3964.91987394354</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8.285240925527694</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>25.7826769471156</v>
+      </c>
+      <c r="J30" t="n">
         <v>16.5411742279832</v>
       </c>
-      <c r="E30" t="n">
+      <c r="K30" t="n">
         <v>43.5362302960951</v>
       </c>
-      <c r="F30" t="n">
-        <v>25.7826769471156</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-2.3298481898334</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3964.91987394354</v>
-      </c>
-      <c r="I30" t="n">
-        <v>87.95340653321141</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>4.528</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>20.1455348442463</v>
       </c>
     </row>
@@ -1561,30 +1653,33 @@
       <c r="B31" t="n">
         <v>2024</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
         <v>0.769118881748846</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
+        <v>5.00871930957159</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4186.4986638365</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8.339620022484397</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>25.5288051289463</v>
+      </c>
+      <c r="J31" t="n">
         <v>-0.42936004906973</v>
       </c>
-      <c r="E31" t="n">
+      <c r="K31" t="n">
         <v>42.3975008711047</v>
       </c>
-      <c r="F31" t="n">
-        <v>25.5288051289463</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5.00871930957159</v>
-      </c>
-      <c r="H31" t="n">
-        <v>4186.4986638365</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>4.239</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>20.2996997058686</v>
       </c>
     </row>
@@ -1605,10 +1700,11 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
         <v>4.005</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
